--- a/output/pdf_financials_xlsx/DAR.xlsx
+++ b/output/pdf_financials_xlsx/DAR.xlsx
@@ -1288,16 +1288,16 @@
         <v>0.416027</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.037324</v>
+        <v>-0.037324</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.673915</v>
+        <v>-0.673915</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.36723</v>
+        <v>-0.36723</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.577371</v>
+        <v>-0.577371</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.450477</v>
@@ -1588,16 +1588,16 @@
         <v>0.416027</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.037324</v>
+        <v>-0.037324</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.673915</v>
+        <v>-0.673915</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.36723</v>
+        <v>-0.36723</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.577371</v>
+        <v>-0.577371</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.450477</v>
@@ -1762,16 +1762,16 @@
         <v>0.416027</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.037324</v>
+        <v>-0.037324</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.673915</v>
+        <v>-0.673915</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.36723</v>
+        <v>-0.36723</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.577371</v>
+        <v>-0.577371</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.450477</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-33.69575</v>
+        <v>33.69575</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>0.416027</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.037324</v>
+        <v>-0.037324</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.673915</v>
+        <v>-0.673915</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.36723</v>
+        <v>-0.36723</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.577371</v>
+        <v>-0.577371</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.450477</v>
@@ -2132,16 +2132,16 @@
         <v>0.416027</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.037324</v>
+        <v>-0.037324</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.673915</v>
+        <v>-0.673915</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.36723</v>
+        <v>-0.36723</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.577371</v>
+        <v>-0.577371</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.450477</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1985.027027027027</v>
+        <v>-1985.027027027027</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>815.2999985879097</v>
+        <v>-815.2999985879097</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-361.9219397756853</v>
@@ -2254,16 +2254,16 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1985.027027027027</v>
+        <v>-1985.027027027027</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>815.2999985879097</v>
+        <v>-815.2999985879097</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>-361.9219397756853</v>
@@ -5913,16 +5913,16 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.706548</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.706548</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.713145</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.117615</v>
       </c>
     </row>
     <row r="93">
@@ -9797,7 +9797,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10508,7 +10512,11 @@
           <t>Reserve (note 5)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11318,7 +11326,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -36481,10 +36493,10 @@
         </is>
       </c>
       <c r="N281" s="5" t="n">
-        <v>0.450477</v>
+        <v>-0.450477</v>
       </c>
       <c r="O281" s="5" t="n">
-        <v>0.529066</v>
+        <v>-0.529066</v>
       </c>
       <c r="P281" s="5" t="n">
         <v>-0.395711</v>
@@ -39237,10 +39249,10 @@
         </is>
       </c>
       <c r="J309" s="5" t="n">
-        <v>0.037324</v>
+        <v>-0.037324</v>
       </c>
       <c r="K309" s="5" t="n">
-        <v>0.673915</v>
+        <v>-0.673915</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -39248,10 +39260,10 @@
         </is>
       </c>
       <c r="M309" s="5" t="n">
-        <v>0.577371</v>
+        <v>-0.577371</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>0.450477</v>
+        <v>-0.450477</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -40544,10 +40556,10 @@
         </is>
       </c>
       <c r="L322" s="5" t="n">
-        <v>0.36723</v>
+        <v>-0.36723</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>0.577371</v>
+        <v>-0.577371</v>
       </c>
       <c r="N322" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DAR.xlsx
+++ b/output/pdf_financials_xlsx/DAR.xlsx
@@ -1041,25 +1041,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.028169</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.015691</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005849</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001441</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003574</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00106</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2001,25 +2001,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.8797509999999999</v>
+        <v>-0.9079199999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.9437179999999999</v>
+        <v>-0.959409</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.734831</v>
+        <v>-0.728982</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.388292</v>
+        <v>-0.389733</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.416027</v>
+        <v>0.412453</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.037324</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.673915</v>
+        <v>-0.672855</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.36723</v>
@@ -2117,25 +2117,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.8797509999999999</v>
+        <v>-0.9079199999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.9437179999999999</v>
+        <v>-0.959409</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.734831</v>
+        <v>-0.728982</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.388292</v>
+        <v>-0.389733</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.416027</v>
+        <v>0.412453</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.037324</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.673915</v>
+        <v>-0.672855</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.36723</v>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-815.6869471693215</v>
+        <v>-841.8046618576966</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-807.3349131256791</v>
+        <v>-820.7583003259391</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-944.9865613868134</v>
+        <v>-937.4647959774179</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1664.108</v>
+        <v>1649.812</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2368,55 +2368,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.017057</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.104169</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.021403</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.00111</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.003606</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.157644</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.07587000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.183379</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.037011</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.011432</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.061484</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.050322</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.092733</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.081659</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.059099</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.003438</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.244341</v>
       </c>
     </row>
     <row r="35">
@@ -2484,55 +2484,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.017057</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.104169</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.021403</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.00111</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.003606</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.157644</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.07587000000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.183379</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.037011</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.011432</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.061484</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.050322</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.092733</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.081659</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.059099</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.003438</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.244341</v>
       </c>
     </row>
     <row r="37">
@@ -3180,49 +3180,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.022619</v>
+        <v>0.005562</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.513015</v>
+        <v>1.408846</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.165018</v>
+        <v>1.143615</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.108644</v>
+        <v>1.107534</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.003606</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.157644</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.078029</v>
+        <v>0.002159</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.185538</v>
+        <v>0.002159</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.03917</v>
+        <v>0.002159</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.011432</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.061484</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.050322</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.095253</v>
+        <v>0.00252</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.081659</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.059099</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -42527,7 +42527,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -44731,7 +44731,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -48838,7 +48838,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" s="5" t="n">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E406" s="5" t="n">

--- a/output/pdf_financials_xlsx/DAR.xlsx
+++ b/output/pdf_financials_xlsx/DAR.xlsx
@@ -6385,13 +6385,13 @@
         <v>-0.018432</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.034248</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.021128</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.001419</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>-0.00263</v>
@@ -6931,19 +6931,19 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.003154</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.003996</v>
       </c>
       <c r="P110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.001267</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.057501</v>
       </c>
     </row>
     <row r="111">
@@ -19178,7 +19178,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -21263,7 +21267,11 @@
           <t>Accretion (note 7)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -21572,7 +21580,11 @@
           <t>Accretion (note 9)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22388,7 +22400,11 @@
           <t>Accretion (note 9)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -23348,7 +23364,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -25128,7 +25148,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
